--- a/assets/constructions/examples/ctd_tsmb_radial_fullround.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_radial_fullround.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,19 +584,48 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BTRR075.066225.LETC</t>
+          <t>MS442GRR050L15RVBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Microscope</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -605,7 +634,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MHC..-6</t>
+          <t>MHC..-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -614,45 +643,45 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2.95</v>
+        <v>1.95</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>5.95</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
-        <v>52</v>
+        <v>32.2</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>VARGUS_D:4</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -689,79 +718,98 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>2815.93</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M552GRR100L20RVBX</t>
+          <t>110.1530.2537TN35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>HORN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>110</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MHC..-5</t>
+          <t>HORN_110-10.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>HORN</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.45</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>4.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>HORN_B110</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -771,12 +819,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>TN35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiN</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -795,14 +843,25 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>Специнструмент</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>PK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTRR075.055220.LETC</t>
+          <t>BTRR050.077230.REA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -819,7 +878,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MHC..-5</t>
+          <t>MHC..-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -828,45 +887,45 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="K4" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>4.95</v>
+        <v>6.95</v>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -876,12 +935,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -903,23 +962,38 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6440.99</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>6440.99</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M552GRR075L20LVBX</t>
+          <t>BTRR100.077230.RETC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Microscope</t>
-        </is>
-      </c>
+          <t>BRICE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>PMKNSH</t>
@@ -928,7 +1002,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MHC..-5</t>
+          <t>MHC..-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -937,45 +1011,45 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>4.95</v>
+        <v>6.95</v>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.75</v>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>VARGUS_D:5</t>
+          <t>VARGUS_D:7</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1012,11 +1086,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5857.91</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>5857.91</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MS442GRR050L15LVBX</t>
+          <t>M662GRR050L25RVBX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1037,7 +1130,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MHC..-4</t>
+          <t>MHC..-6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1046,30 +1139,30 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>2.95</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>5.95</v>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O6" t="n">
-        <v>32.2</v>
+        <v>52</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1079,12 +1172,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>VARGUS_D:4</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1119,6 +1212,25 @@
       <c r="AE6" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>3822.6</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
